--- a/data/odds/Game of Yards! 2026 Betting Odds.xlsx
+++ b/data/odds/Game of Yards! 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="57">
   <si>
     <t>Record</t>
   </si>
@@ -36,106 +36,106 @@
     <t>Team HebAchi</t>
   </si>
   <si>
+    <t>Groot-o-Matic</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>Vellapanti</t>
+  </si>
+  <si>
     <t>Vidhi's Spirited Team</t>
   </si>
   <si>
-    <t>Groot-o-Matic</t>
+    <t>Brown Munde</t>
   </si>
   <si>
     <t>The Chase is on</t>
   </si>
   <si>
-    <t>Brown Munde</t>
-  </si>
-  <si>
-    <t>BB</t>
+    <t>JAWN Doe</t>
   </si>
   <si>
     <t>Wakanda Forever</t>
   </si>
   <si>
-    <t>Vellapanti</t>
-  </si>
-  <si>
-    <t>JAWN Doe</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>96.5%</t>
-  </si>
-  <si>
-    <t>93.6%</t>
-  </si>
-  <si>
-    <t>71.1%</t>
-  </si>
-  <si>
-    <t>53.6%</t>
-  </si>
-  <si>
-    <t>50.0%</t>
-  </si>
-  <si>
-    <t>21.4%</t>
-  </si>
-  <si>
-    <t>10.5%</t>
-  </si>
-  <si>
-    <t>3.3%</t>
-  </si>
-  <si>
-    <t>-∞</t>
-  </si>
-  <si>
-    <t>-2757</t>
-  </si>
-  <si>
-    <t>-1462</t>
-  </si>
-  <si>
-    <t>-246</t>
-  </si>
-  <si>
-    <t>-116</t>
-  </si>
-  <si>
-    <t>-100</t>
-  </si>
-  <si>
-    <t>+367</t>
-  </si>
-  <si>
-    <t>+852</t>
-  </si>
-  <si>
-    <t>+2930</t>
+    <t>99.9%</t>
+  </si>
+  <si>
+    <t>89.4%</t>
+  </si>
+  <si>
+    <t>87.4%</t>
+  </si>
+  <si>
+    <t>81.3%</t>
+  </si>
+  <si>
+    <t>65.0%</t>
+  </si>
+  <si>
+    <t>38.0%</t>
+  </si>
+  <si>
+    <t>36.2%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-843</t>
+  </si>
+  <si>
+    <t>-694</t>
+  </si>
+  <si>
+    <t>-435</t>
+  </si>
+  <si>
+    <t>-186</t>
+  </si>
+  <si>
+    <t>+163</t>
+  </si>
+  <si>
+    <t>+176</t>
+  </si>
+  <si>
+    <t>+7043</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>62.8%</t>
-  </si>
-  <si>
-    <t>26.9%</t>
-  </si>
-  <si>
-    <t>5.2%</t>
-  </si>
-  <si>
-    <t>4.7%</t>
+    <t>50.9%</t>
+  </si>
+  <si>
+    <t>47.8%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -147,16 +147,16 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-169</t>
-  </si>
-  <si>
-    <t>+272</t>
-  </si>
-  <si>
-    <t>+1823</t>
-  </si>
-  <si>
-    <t>+2028</t>
+    <t>-104</t>
+  </si>
+  <si>
+    <t>+109</t>
+  </si>
+  <si>
+    <t>+16567</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
   <si>
     <t>+49900</t>
@@ -165,49 +165,28 @@
     <t>+99900</t>
   </si>
   <si>
-    <t>+∞</t>
-  </si>
-  <si>
-    <t>50.3%</t>
-  </si>
-  <si>
-    <t>24.2%</t>
-  </si>
-  <si>
-    <t>17.4%</t>
-  </si>
-  <si>
-    <t>4.0%</t>
-  </si>
-  <si>
-    <t>2.3%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>-101</t>
-  </si>
-  <si>
-    <t>+313</t>
-  </si>
-  <si>
-    <t>+475</t>
-  </si>
-  <si>
-    <t>+2400</t>
-  </si>
-  <si>
-    <t>+4248</t>
-  </si>
-  <si>
-    <t>+7043</t>
-  </si>
-  <si>
-    <t>+33233</t>
+    <t>50.4%</t>
+  </si>
+  <si>
+    <t>44.0%</t>
+  </si>
+  <si>
+    <t>3.7%</t>
+  </si>
+  <si>
+    <t>1.6%</t>
+  </si>
+  <si>
+    <t>-102</t>
+  </si>
+  <si>
+    <t>+127</t>
+  </si>
+  <si>
+    <t>+2603</t>
+  </si>
+  <si>
+    <t>+6150</t>
   </si>
 </sst>
 </file>
@@ -590,10 +569,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -601,13 +580,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -615,13 +594,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -632,10 +611,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -643,13 +622,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -657,13 +636,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -671,13 +650,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -685,13 +664,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -699,13 +678,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -713,10 +692,10 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
         <v>34</v>
@@ -751,7 +730,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
         <v>36</v>
@@ -776,10 +755,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>38</v>
@@ -790,7 +769,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -807,7 +786,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
@@ -821,7 +800,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>41</v>
@@ -832,13 +811,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
         <v>48</v>
@@ -846,44 +825,44 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -915,13 +894,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -929,13 +908,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -943,13 +922,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -957,41 +936,41 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1002,10 +981,10 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1013,10 +992,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
         <v>48</v>
@@ -1033,7 +1012,7 @@
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1041,13 +1020,13 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Game of Yards! 2026 Betting Odds.xlsx
+++ b/data/odds/Game of Yards! 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="65">
   <si>
     <t>Record</t>
   </si>
@@ -33,109 +33,118 @@
     <t>Pain Inflictors</t>
   </si>
   <si>
+    <t>Groot-o-Matic</t>
+  </si>
+  <si>
     <t>Team HebAchi</t>
   </si>
   <si>
-    <t>Groot-o-Matic</t>
+    <t>Vidhi's Spirited Team</t>
+  </si>
+  <si>
+    <t>Vellapanti</t>
   </si>
   <si>
     <t>BB</t>
   </si>
   <si>
-    <t>Vellapanti</t>
-  </si>
-  <si>
-    <t>Vidhi's Spirited Team</t>
-  </si>
-  <si>
     <t>Brown Munde</t>
   </si>
   <si>
+    <t>Wakanda Forever</t>
+  </si>
+  <si>
+    <t>JAWN Doe</t>
+  </si>
+  <si>
     <t>The Chase is on</t>
   </si>
   <si>
-    <t>JAWN Doe</t>
-  </si>
-  <si>
-    <t>Wakanda Forever</t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.9%</t>
-  </si>
-  <si>
-    <t>89.4%</t>
-  </si>
-  <si>
-    <t>87.4%</t>
-  </si>
-  <si>
-    <t>81.3%</t>
-  </si>
-  <si>
-    <t>65.0%</t>
-  </si>
-  <si>
-    <t>38.0%</t>
-  </si>
-  <si>
-    <t>36.2%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
+    <t>99.5%</t>
+  </si>
+  <si>
+    <t>97.5%</t>
+  </si>
+  <si>
+    <t>67.5%</t>
+  </si>
+  <si>
+    <t>64.1%</t>
+  </si>
+  <si>
+    <t>59.4%</t>
+  </si>
+  <si>
+    <t>45.6%</t>
+  </si>
+  <si>
+    <t>27.8%</t>
+  </si>
+  <si>
+    <t>23.4%</t>
+  </si>
+  <si>
+    <t>15.2%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-843</t>
-  </si>
-  <si>
-    <t>-694</t>
-  </si>
-  <si>
-    <t>-435</t>
-  </si>
-  <si>
-    <t>-186</t>
-  </si>
-  <si>
-    <t>+163</t>
-  </si>
-  <si>
-    <t>+176</t>
-  </si>
-  <si>
-    <t>+7043</t>
+    <t>-19900</t>
+  </si>
+  <si>
+    <t>-3900</t>
+  </si>
+  <si>
+    <t>-208</t>
+  </si>
+  <si>
+    <t>-179</t>
+  </si>
+  <si>
+    <t>-146</t>
+  </si>
+  <si>
+    <t>+119</t>
+  </si>
+  <si>
+    <t>+260</t>
+  </si>
+  <si>
+    <t>+327</t>
+  </si>
+  <si>
+    <t>+558</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>50.9%</t>
-  </si>
-  <si>
-    <t>47.8%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
+    <t>77.8%</t>
+  </si>
+  <si>
+    <t>18.2%</t>
+  </si>
+  <si>
+    <t>3.7%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -147,16 +156,13 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-104</t>
-  </si>
-  <si>
-    <t>+109</t>
-  </si>
-  <si>
-    <t>+16567</t>
-  </si>
-  <si>
-    <t>+24900</t>
+    <t>-350</t>
+  </si>
+  <si>
+    <t>+449</t>
+  </si>
+  <si>
+    <t>+2603</t>
   </si>
   <si>
     <t>+49900</t>
@@ -165,28 +171,46 @@
     <t>+99900</t>
   </si>
   <si>
-    <t>50.4%</t>
-  </si>
-  <si>
-    <t>44.0%</t>
-  </si>
-  <si>
-    <t>3.7%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
-  </si>
-  <si>
-    <t>-102</t>
-  </si>
-  <si>
-    <t>+127</t>
-  </si>
-  <si>
-    <t>+2603</t>
-  </si>
-  <si>
-    <t>+6150</t>
+    <t>31.8%</t>
+  </si>
+  <si>
+    <t>24.0%</t>
+  </si>
+  <si>
+    <t>22.2%</t>
+  </si>
+  <si>
+    <t>8.5%</t>
+  </si>
+  <si>
+    <t>6.6%</t>
+  </si>
+  <si>
+    <t>4.3%</t>
+  </si>
+  <si>
+    <t>2.6%</t>
+  </si>
+  <si>
+    <t>+214</t>
+  </si>
+  <si>
+    <t>+317</t>
+  </si>
+  <si>
+    <t>+350</t>
+  </si>
+  <si>
+    <t>+1076</t>
+  </si>
+  <si>
+    <t>+1415</t>
+  </si>
+  <si>
+    <t>+2226</t>
+  </si>
+  <si>
+    <t>+3746</t>
   </si>
 </sst>
 </file>
@@ -569,10 +593,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -583,10 +607,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -594,13 +618,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -611,10 +635,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -622,13 +646,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -636,13 +660,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -650,13 +674,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -667,10 +691,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -681,10 +705,10 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -692,13 +716,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -727,58 +751,58 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -786,55 +810,55 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -842,27 +866,27 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -883,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -894,13 +918,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -911,10 +935,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -925,10 +949,10 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -936,41 +960,41 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -981,24 +1005,24 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1009,24 +1033,24 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Game of Yards! 2026 Betting Odds.xlsx
+++ b/data/odds/Game of Yards! 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
   <si>
     <t>Record</t>
   </si>
@@ -33,118 +33,121 @@
     <t>Pain Inflictors</t>
   </si>
   <si>
+    <t>Team HebAchi</t>
+  </si>
+  <si>
     <t>Groot-o-Matic</t>
   </si>
   <si>
-    <t>Team HebAchi</t>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>Vellapanti</t>
   </si>
   <si>
     <t>Vidhi's Spirited Team</t>
   </si>
   <si>
-    <t>Vellapanti</t>
-  </si>
-  <si>
-    <t>BB</t>
+    <t>Wakanda Forever</t>
+  </si>
+  <si>
+    <t>The Chase is on</t>
+  </si>
+  <si>
+    <t>JAWN Doe</t>
   </si>
   <si>
     <t>Brown Munde</t>
   </si>
   <si>
-    <t>Wakanda Forever</t>
-  </si>
-  <si>
-    <t>JAWN Doe</t>
-  </si>
-  <si>
-    <t>The Chase is on</t>
-  </si>
-  <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.5%</t>
-  </si>
-  <si>
-    <t>97.5%</t>
-  </si>
-  <si>
-    <t>67.5%</t>
-  </si>
-  <si>
-    <t>64.1%</t>
-  </si>
-  <si>
-    <t>59.4%</t>
-  </si>
-  <si>
-    <t>45.6%</t>
-  </si>
-  <si>
-    <t>27.8%</t>
-  </si>
-  <si>
-    <t>23.4%</t>
-  </si>
-  <si>
-    <t>15.2%</t>
+    <t>99.6%</t>
+  </si>
+  <si>
+    <t>96.6%</t>
+  </si>
+  <si>
+    <t>79.2%</t>
+  </si>
+  <si>
+    <t>78.6%</t>
+  </si>
+  <si>
+    <t>63.3%</t>
+  </si>
+  <si>
+    <t>39.0%</t>
+  </si>
+  <si>
+    <t>25.6%</t>
+  </si>
+  <si>
+    <t>9.2%</t>
+  </si>
+  <si>
+    <t>8.9%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-19900</t>
-  </si>
-  <si>
-    <t>-3900</t>
-  </si>
-  <si>
-    <t>-208</t>
-  </si>
-  <si>
-    <t>-179</t>
-  </si>
-  <si>
-    <t>-146</t>
-  </si>
-  <si>
-    <t>+119</t>
-  </si>
-  <si>
-    <t>+260</t>
-  </si>
-  <si>
-    <t>+327</t>
-  </si>
-  <si>
-    <t>+558</t>
+    <t>-24900</t>
+  </si>
+  <si>
+    <t>-2841</t>
+  </si>
+  <si>
+    <t>-381</t>
+  </si>
+  <si>
+    <t>-367</t>
+  </si>
+  <si>
+    <t>-172</t>
+  </si>
+  <si>
+    <t>+156</t>
+  </si>
+  <si>
+    <t>+291</t>
+  </si>
+  <si>
+    <t>+987</t>
+  </si>
+  <si>
+    <t>+1024</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>77.8%</t>
-  </si>
-  <si>
-    <t>18.2%</t>
-  </si>
-  <si>
-    <t>3.7%</t>
+    <t>56.6%</t>
+  </si>
+  <si>
+    <t>30.6%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>0.9%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -156,13 +159,19 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-350</t>
-  </si>
-  <si>
-    <t>+449</t>
-  </si>
-  <si>
-    <t>+2603</t>
+    <t>-130</t>
+  </si>
+  <si>
+    <t>+227</t>
+  </si>
+  <si>
+    <t>+826</t>
+  </si>
+  <si>
+    <t>+11011</t>
+  </si>
+  <si>
+    <t>+12400</t>
   </si>
   <si>
     <t>+49900</t>
@@ -171,46 +180,40 @@
     <t>+99900</t>
   </si>
   <si>
-    <t>31.8%</t>
-  </si>
-  <si>
-    <t>24.0%</t>
-  </si>
-  <si>
-    <t>22.2%</t>
-  </si>
-  <si>
-    <t>8.5%</t>
-  </si>
-  <si>
-    <t>6.6%</t>
-  </si>
-  <si>
-    <t>4.3%</t>
+    <t>36.8%</t>
+  </si>
+  <si>
+    <t>35.8%</t>
+  </si>
+  <si>
+    <t>13.8%</t>
   </si>
   <si>
     <t>2.6%</t>
   </si>
   <si>
-    <t>+214</t>
-  </si>
-  <si>
-    <t>+317</t>
-  </si>
-  <si>
-    <t>+350</t>
-  </si>
-  <si>
-    <t>+1076</t>
-  </si>
-  <si>
-    <t>+1415</t>
-  </si>
-  <si>
-    <t>+2226</t>
+    <t>1.1%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>+172</t>
+  </si>
+  <si>
+    <t>+179</t>
+  </si>
+  <si>
+    <t>+625</t>
   </si>
   <si>
     <t>+3746</t>
+  </si>
+  <si>
+    <t>+8991</t>
+  </si>
+  <si>
+    <t>+16567</t>
   </si>
 </sst>
 </file>
@@ -593,10 +596,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -607,10 +610,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -618,13 +621,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -635,10 +638,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -646,13 +649,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -660,13 +663,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -674,13 +677,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -691,10 +694,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -705,10 +708,10 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -716,13 +719,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -743,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -757,10 +760,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -771,10 +774,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -782,55 +785,55 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -838,27 +841,27 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -866,27 +869,27 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -907,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -918,13 +921,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -935,10 +938,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -949,10 +952,10 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -960,13 +963,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -974,46 +977,46 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -1022,7 +1025,7 @@
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1033,24 +1036,24 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Game of Yards! 2026 Betting Odds.xlsx
+++ b/data/odds/Game of Yards! 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="67">
   <si>
     <t>Record</t>
   </si>
@@ -39,67 +39,70 @@
     <t>Groot-o-Matic</t>
   </si>
   <si>
+    <t>Vidhi's Spirited Team</t>
+  </si>
+  <si>
+    <t>Wakanda Forever</t>
+  </si>
+  <si>
+    <t>Vellapanti</t>
+  </si>
+  <si>
     <t>BB</t>
   </si>
   <si>
-    <t>Vellapanti</t>
-  </si>
-  <si>
-    <t>Vidhi's Spirited Team</t>
-  </si>
-  <si>
-    <t>Wakanda Forever</t>
-  </si>
-  <si>
     <t>The Chase is on</t>
   </si>
   <si>
+    <t>Brown Munde</t>
+  </si>
+  <si>
     <t>JAWN Doe</t>
   </si>
   <si>
-    <t>Brown Munde</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>100.0%</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>99.9%</t>
   </si>
   <si>
     <t>99.6%</t>
   </si>
   <si>
-    <t>96.6%</t>
-  </si>
-  <si>
-    <t>79.2%</t>
-  </si>
-  <si>
-    <t>78.6%</t>
-  </si>
-  <si>
-    <t>63.3%</t>
-  </si>
-  <si>
-    <t>39.0%</t>
-  </si>
-  <si>
-    <t>25.6%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>8.9%</t>
+    <t>90.9%</t>
+  </si>
+  <si>
+    <t>86.0%</t>
+  </si>
+  <si>
+    <t>81.6%</t>
+  </si>
+  <si>
+    <t>58.6%</t>
+  </si>
+  <si>
+    <t>49.6%</t>
+  </si>
+  <si>
+    <t>26.2%</t>
+  </si>
+  <si>
+    <t>5.4%</t>
+  </si>
+  <si>
+    <t>2.2%</t>
   </si>
   <si>
     <t>-99900</t>
@@ -108,49 +111,46 @@
     <t>-24900</t>
   </si>
   <si>
-    <t>-2841</t>
-  </si>
-  <si>
-    <t>-381</t>
-  </si>
-  <si>
-    <t>-367</t>
-  </si>
-  <si>
-    <t>-172</t>
-  </si>
-  <si>
-    <t>+156</t>
-  </si>
-  <si>
-    <t>+291</t>
-  </si>
-  <si>
-    <t>+987</t>
-  </si>
-  <si>
-    <t>+1024</t>
+    <t>-999</t>
+  </si>
+  <si>
+    <t>-614</t>
+  </si>
+  <si>
+    <t>-443</t>
+  </si>
+  <si>
+    <t>-142</t>
+  </si>
+  <si>
+    <t>+102</t>
+  </si>
+  <si>
+    <t>+282</t>
+  </si>
+  <si>
+    <t>+1752</t>
+  </si>
+  <si>
+    <t>+4445</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>56.6%</t>
-  </si>
-  <si>
-    <t>30.6%</t>
-  </si>
-  <si>
-    <t>10.8%</t>
-  </si>
-  <si>
-    <t>0.9%</t>
-  </si>
-  <si>
-    <t>0.8%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
+    <t>72.3%</t>
+  </si>
+  <si>
+    <t>22.5%</t>
+  </si>
+  <si>
+    <t>1.9%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
   </si>
   <si>
     <t>0.1%</t>
@@ -159,61 +159,64 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-130</t>
-  </si>
-  <si>
-    <t>+227</t>
-  </si>
-  <si>
-    <t>+826</t>
-  </si>
-  <si>
-    <t>+11011</t>
-  </si>
-  <si>
-    <t>+12400</t>
-  </si>
-  <si>
-    <t>+49900</t>
+    <t>-261</t>
+  </si>
+  <si>
+    <t>+344</t>
+  </si>
+  <si>
+    <t>+5163</t>
+  </si>
+  <si>
+    <t>+5782</t>
+  </si>
+  <si>
+    <t>+6567</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>36.8%</t>
-  </si>
-  <si>
-    <t>35.8%</t>
-  </si>
-  <si>
-    <t>13.8%</t>
-  </si>
-  <si>
-    <t>2.6%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
+    <t>52.9%</t>
+  </si>
+  <si>
+    <t>35.5%</t>
+  </si>
+  <si>
+    <t>5.9%</t>
+  </si>
+  <si>
+    <t>3.3%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
   </si>
   <si>
     <t>0.6%</t>
   </si>
   <si>
-    <t>+172</t>
-  </si>
-  <si>
-    <t>+179</t>
-  </si>
-  <si>
-    <t>+625</t>
-  </si>
-  <si>
-    <t>+3746</t>
-  </si>
-  <si>
-    <t>+8991</t>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>-112</t>
+  </si>
+  <si>
+    <t>+182</t>
+  </si>
+  <si>
+    <t>+1595</t>
+  </si>
+  <si>
+    <t>+2930</t>
+  </si>
+  <si>
+    <t>+7043</t>
   </si>
   <si>
     <t>+16567</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
 </sst>
 </file>
@@ -596,10 +599,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -610,10 +613,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -621,13 +624,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -638,10 +641,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -649,13 +652,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -663,13 +666,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -680,10 +683,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -694,10 +697,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -705,13 +708,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -722,10 +725,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -746,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -760,7 +763,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
         <v>47</v>
@@ -774,7 +777,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
         <v>48</v>
@@ -785,10 +788,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
         <v>49</v>
@@ -796,13 +799,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
         <v>50</v>
@@ -810,13 +813,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
@@ -824,13 +827,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
         <v>52</v>
@@ -838,16 +841,16 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -855,18 +858,18 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -875,21 +878,21 @@
         <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -910,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -924,7 +927,7 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
         <v>60</v>
@@ -935,10 +938,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
         <v>61</v>
@@ -952,7 +955,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
         <v>62</v>
@@ -966,10 +969,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -977,32 +980,32 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -1011,7 +1014,7 @@
         <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1019,13 +1022,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1039,7 +1042,7 @@
         <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1053,7 +1056,7 @@
         <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Game of Yards! 2026 Betting Odds.xlsx
+++ b/data/odds/Game of Yards! 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
   <si>
     <t>Record</t>
   </si>
@@ -36,15 +36,15 @@
     <t>Team HebAchi</t>
   </si>
   <si>
+    <t>Vidhi's Spirited Team</t>
+  </si>
+  <si>
+    <t>Wakanda Forever</t>
+  </si>
+  <si>
     <t>Groot-o-Matic</t>
   </si>
   <si>
-    <t>Vidhi's Spirited Team</t>
-  </si>
-  <si>
-    <t>Wakanda Forever</t>
-  </si>
-  <si>
     <t>Vellapanti</t>
   </si>
   <si>
@@ -60,97 +60,97 @@
     <t>JAWN Doe</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>99.9%</t>
-  </si>
-  <si>
-    <t>99.6%</t>
-  </si>
-  <si>
-    <t>90.9%</t>
-  </si>
-  <si>
-    <t>86.0%</t>
-  </si>
-  <si>
-    <t>81.6%</t>
-  </si>
-  <si>
-    <t>58.6%</t>
-  </si>
-  <si>
-    <t>49.6%</t>
-  </si>
-  <si>
-    <t>26.2%</t>
-  </si>
-  <si>
-    <t>5.4%</t>
-  </si>
-  <si>
-    <t>2.2%</t>
-  </si>
-  <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-24900</t>
-  </si>
-  <si>
-    <t>-999</t>
-  </si>
-  <si>
-    <t>-614</t>
-  </si>
-  <si>
-    <t>-443</t>
-  </si>
-  <si>
-    <t>-142</t>
-  </si>
-  <si>
-    <t>+102</t>
-  </si>
-  <si>
-    <t>+282</t>
-  </si>
-  <si>
-    <t>+1752</t>
-  </si>
-  <si>
-    <t>+4445</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>99.4%</t>
+  </si>
+  <si>
+    <t>96.5%</t>
+  </si>
+  <si>
+    <t>92.7%</t>
+  </si>
+  <si>
+    <t>89.9%</t>
+  </si>
+  <si>
+    <t>84.5%</t>
+  </si>
+  <si>
+    <t>77.1%</t>
+  </si>
+  <si>
+    <t>38.1%</t>
+  </si>
+  <si>
+    <t>13.0%</t>
+  </si>
+  <si>
+    <t>8.5%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>-16567</t>
+  </si>
+  <si>
+    <t>-2757</t>
+  </si>
+  <si>
+    <t>-1270</t>
+  </si>
+  <si>
+    <t>-890</t>
+  </si>
+  <si>
+    <t>-545</t>
+  </si>
+  <si>
+    <t>-337</t>
+  </si>
+  <si>
+    <t>+162</t>
+  </si>
+  <si>
+    <t>+669</t>
+  </si>
+  <si>
+    <t>+1076</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>72.3%</t>
-  </si>
-  <si>
-    <t>22.5%</t>
-  </si>
-  <si>
-    <t>1.9%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
-  </si>
-  <si>
-    <t>1.5%</t>
+    <t>57.8%</t>
+  </si>
+  <si>
+    <t>20.8%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>5.9%</t>
+  </si>
+  <si>
+    <t>4.2%</t>
+  </si>
+  <si>
+    <t>1.8%</t>
   </si>
   <si>
     <t>0.1%</t>
@@ -159,64 +159,49 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-261</t>
-  </si>
-  <si>
-    <t>+344</t>
-  </si>
-  <si>
-    <t>+5163</t>
-  </si>
-  <si>
-    <t>+5782</t>
-  </si>
-  <si>
-    <t>+6567</t>
+    <t>-137</t>
+  </si>
+  <si>
+    <t>+381</t>
+  </si>
+  <si>
+    <t>+999</t>
+  </si>
+  <si>
+    <t>+1595</t>
+  </si>
+  <si>
+    <t>+2281</t>
+  </si>
+  <si>
+    <t>+5456</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>52.9%</t>
-  </si>
-  <si>
-    <t>35.5%</t>
-  </si>
-  <si>
-    <t>5.9%</t>
-  </si>
-  <si>
-    <t>3.3%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>-112</t>
-  </si>
-  <si>
-    <t>+182</t>
-  </si>
-  <si>
-    <t>+1595</t>
-  </si>
-  <si>
-    <t>+2930</t>
-  </si>
-  <si>
-    <t>+7043</t>
-  </si>
-  <si>
-    <t>+16567</t>
-  </si>
-  <si>
-    <t>+33233</t>
+    <t>75.3%</t>
+  </si>
+  <si>
+    <t>12.9%</t>
+  </si>
+  <si>
+    <t>10.0%</t>
+  </si>
+  <si>
+    <t>1.6%</t>
+  </si>
+  <si>
+    <t>-305</t>
+  </si>
+  <si>
+    <t>+675</t>
+  </si>
+  <si>
+    <t>+900</t>
+  </si>
+  <si>
+    <t>+6150</t>
   </si>
 </sst>
 </file>
@@ -599,10 +584,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -613,10 +598,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -624,13 +609,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -641,10 +626,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -652,13 +637,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -666,13 +651,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -683,10 +668,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -697,10 +682,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -708,13 +693,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -725,10 +710,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -749,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -763,7 +748,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>47</v>
@@ -777,7 +762,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>48</v>
@@ -788,10 +773,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>49</v>
@@ -805,7 +790,7 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
         <v>50</v>
@@ -816,10 +801,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
@@ -827,13 +812,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>52</v>
@@ -841,35 +826,35 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -878,21 +863,21 @@
         <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -913,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -927,10 +912,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -938,13 +923,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -955,10 +940,10 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -969,10 +954,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -980,55 +965,55 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1042,21 +1027,21 @@
         <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Game of Yards! 2026 Betting Odds.xlsx
+++ b/data/odds/Game of Yards! 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="65">
   <si>
     <t>Record</t>
   </si>
@@ -72,136 +72,145 @@
     <t>2-5</t>
   </si>
   <si>
-    <t>99.4%</t>
-  </si>
-  <si>
-    <t>96.5%</t>
-  </si>
-  <si>
-    <t>92.7%</t>
-  </si>
-  <si>
-    <t>89.9%</t>
-  </si>
-  <si>
-    <t>84.5%</t>
-  </si>
-  <si>
-    <t>77.1%</t>
-  </si>
-  <si>
-    <t>38.1%</t>
-  </si>
-  <si>
-    <t>13.0%</t>
-  </si>
-  <si>
-    <t>8.5%</t>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>96.9%</t>
+  </si>
+  <si>
+    <t>91.9%</t>
+  </si>
+  <si>
+    <t>86.8%</t>
+  </si>
+  <si>
+    <t>83.1%</t>
+  </si>
+  <si>
+    <t>77.8%</t>
+  </si>
+  <si>
+    <t>42.6%</t>
+  </si>
+  <si>
+    <t>14.0%</t>
+  </si>
+  <si>
+    <t>6.7%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>-49900</t>
+  </si>
+  <si>
+    <t>-3126</t>
+  </si>
+  <si>
+    <t>-1135</t>
+  </si>
+  <si>
+    <t>-658</t>
+  </si>
+  <si>
+    <t>-492</t>
+  </si>
+  <si>
+    <t>-350</t>
+  </si>
+  <si>
+    <t>+135</t>
+  </si>
+  <si>
+    <t>+614</t>
+  </si>
+  <si>
+    <t>+1393</t>
+  </si>
+  <si>
+    <t>+24900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>59.3%</t>
+  </si>
+  <si>
+    <t>19.7%</t>
+  </si>
+  <si>
+    <t>8.4%</t>
+  </si>
+  <si>
+    <t>6.2%</t>
+  </si>
+  <si>
+    <t>4.4%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
   </si>
   <si>
     <t>0.3%</t>
   </si>
   <si>
-    <t>-16567</t>
-  </si>
-  <si>
-    <t>-2757</t>
-  </si>
-  <si>
-    <t>-1270</t>
-  </si>
-  <si>
-    <t>-890</t>
-  </si>
-  <si>
-    <t>-545</t>
-  </si>
-  <si>
-    <t>-337</t>
-  </si>
-  <si>
-    <t>+162</t>
-  </si>
-  <si>
-    <t>+669</t>
-  </si>
-  <si>
-    <t>+1076</t>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-146</t>
+  </si>
+  <si>
+    <t>+408</t>
+  </si>
+  <si>
+    <t>+1090</t>
+  </si>
+  <si>
+    <t>+1513</t>
+  </si>
+  <si>
+    <t>+2173</t>
+  </si>
+  <si>
+    <t>+5782</t>
   </si>
   <si>
     <t>+33233</t>
   </si>
   <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>57.8%</t>
-  </si>
-  <si>
-    <t>20.8%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>5.9%</t>
-  </si>
-  <si>
-    <t>4.2%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-137</t>
-  </si>
-  <si>
-    <t>+381</t>
-  </si>
-  <si>
-    <t>+999</t>
-  </si>
-  <si>
-    <t>+1595</t>
-  </si>
-  <si>
-    <t>+2281</t>
-  </si>
-  <si>
-    <t>+5456</t>
-  </si>
-  <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>75.3%</t>
-  </si>
-  <si>
-    <t>12.9%</t>
-  </si>
-  <si>
-    <t>10.0%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
-  </si>
-  <si>
-    <t>-305</t>
-  </si>
-  <si>
-    <t>+675</t>
-  </si>
-  <si>
-    <t>+900</t>
-  </si>
-  <si>
-    <t>+6150</t>
+    <t>75.7%</t>
+  </si>
+  <si>
+    <t>12.8%</t>
+  </si>
+  <si>
+    <t>9.5%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>-312</t>
+  </si>
+  <si>
+    <t>+681</t>
+  </si>
+  <si>
+    <t>+953</t>
+  </si>
+  <si>
+    <t>+7043</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -832,29 +841,29 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -863,12 +872,12 @@
         <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -877,7 +886,7 @@
         <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -912,10 +921,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -926,10 +935,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -940,10 +949,10 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -954,10 +963,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -968,29 +977,29 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -999,26 +1008,26 @@
         <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1027,21 +1036,21 @@
         <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
